--- a/src/test/resources/testData/LoginData.xlsx
+++ b/src/test/resources/testData/LoginData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t xml:space="preserve">username</t>
   </si>
@@ -32,6 +32,39 @@
   </si>
   <si>
     <t xml:space="preserve">test2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jsdhsjdh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdfsdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdfsdss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdfdsdsfsd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdfdsfds</t>
   </si>
 </sst>
 </file>
@@ -257,7 +290,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
@@ -285,6 +318,54 @@
       </c>
       <c r="B3" s="3" t="n">
         <v>4321</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testData/LoginData.xlsx
+++ b/src/test/resources/testData/LoginData.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="15">
   <si>
     <t xml:space="preserve">username</t>
   </si>
@@ -80,6 +81,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -101,11 +103,13 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -155,15 +159,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -377,4 +381,95 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/src/test/resources/testData/LoginData.xlsx
+++ b/src/test/resources/testData/LoginData.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
   <si>
     <t xml:space="preserve">username</t>
   </si>
@@ -33,39 +33,6 @@
   </si>
   <si>
     <t xml:space="preserve">test2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jsdhsjdh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdfsdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdfsdss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdfdsdsfsd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdfdsfds</t>
   </si>
 </sst>
 </file>
@@ -294,7 +261,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
@@ -325,52 +292,32 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A4" s="0"/>
+      <c r="B4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A5" s="0"/>
+      <c r="B5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A6" s="0"/>
+      <c r="B6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A7" s="0"/>
+      <c r="B7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0"/>
+      <c r="B10" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -388,7 +335,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -413,54 +360,6 @@
       </c>
       <c r="B3" s="3" t="n">
         <v>4321</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
